--- a/arch/migracao_oci_aws.xlsx
+++ b/arch/migracao_oci_aws.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\clayton.oliveira\source\repos\files\arch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B443FC2D-FC1B-483F-B7FF-22483B7DA9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2926C10-FFBC-4250-BF3A-5B684CFD06B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Comparativo Mensal" sheetId="2" r:id="rId1"/>
-    <sheet name="Quick Wins" sheetId="3" r:id="rId2"/>
-    <sheet name="Custos de Migração" sheetId="4" r:id="rId3"/>
+    <sheet name="Custo - OCI" sheetId="5" r:id="rId1"/>
+    <sheet name="Comparativo Mensal" sheetId="2" r:id="rId2"/>
+    <sheet name="Quick Wins" sheetId="3" r:id="rId3"/>
+    <sheet name="Custos de Migração" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="155">
   <si>
     <t>Economia Mensal</t>
   </si>
@@ -118,9 +119,6 @@
     <t>Amazon Aurora MySQL</t>
   </si>
   <si>
-    <t>Substitui Oracle + MySQL OCI</t>
-  </si>
-  <si>
     <t>Amazon ElastiCache (Redis)</t>
   </si>
   <si>
@@ -193,9 +191,6 @@
     <t>Egress / Tráfego de rede (AWS)</t>
   </si>
   <si>
-    <t>AWS egress tipicamente mais caro</t>
-  </si>
-  <si>
     <t>VPN / Interconexão OCI</t>
   </si>
   <si>
@@ -455,18 +450,73 @@
   </si>
   <si>
     <t>Valor Hora(R$)</t>
+  </si>
+  <si>
+    <t>VMs (QTD)</t>
+  </si>
+  <si>
+    <t>Familia O.S.</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Computação</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>Data Transfer</t>
+  </si>
+  <si>
+    <t>Load Balancer</t>
+  </si>
+  <si>
+    <t>IP Address</t>
+  </si>
+  <si>
+    <t>Windows</t>
+  </si>
+  <si>
+    <t>Linux</t>
+  </si>
+  <si>
+    <t>Total Geral</t>
+  </si>
+  <si>
+    <t>Appliances</t>
+  </si>
+  <si>
+    <t>Custo Aprox. p/ VM</t>
+  </si>
+  <si>
+    <t>10% em media do total do valor de storage OCI</t>
+  </si>
+  <si>
+    <t>Apps AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS egress </t>
+  </si>
+  <si>
+    <t>Custo Aprox. p/ VM APPs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;R$ &quot;#,##0.00;&quot;(R$ &quot;#,##0.00\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0&quot; meses&quot;"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -562,6 +612,12 @@
       <sz val="16"/>
       <color rgb="FF006100"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -702,10 +758,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -717,7 +774,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -736,7 +792,6 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -792,8 +847,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -807,6 +866,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>68888</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>234995</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD0EC5C7-C4CB-9DA2-25DA-AD9293606494}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="2450138"/>
+          <a:ext cx="10296570" cy="4388812"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1006,1107 +1131,1200 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DB2872-B59A-4F5F-AB28-F508AD4F426A}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.26953125" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" customWidth="1"/>
+    <col min="4" max="4" width="17.6328125" customWidth="1"/>
+    <col min="5" max="5" width="24.453125" customWidth="1"/>
+    <col min="6" max="6" width="37.6328125" customWidth="1"/>
+    <col min="10" max="10" width="16.08984375" customWidth="1"/>
+    <col min="11" max="11" width="19.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J2" s="36">
+        <v>8757</v>
+      </c>
+      <c r="K2" s="36">
+        <f>A2*J2</f>
+        <v>507906</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="36">
+        <v>294389.15000000002</v>
+      </c>
+      <c r="D8" s="37">
+        <f>SUM(B8:B12)</f>
+        <v>365147.57</v>
+      </c>
+      <c r="E8" s="37">
+        <f>D8 / (SUM(A2:A4))</f>
+        <v>2501.0107534246577</v>
+      </c>
+      <c r="F8" s="37">
+        <f>25*E8</f>
+        <v>62525.268835616444</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="36">
+        <v>52116.93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B10" s="36">
+        <v>12333.58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" s="36">
+        <v>4212.22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="36">
+        <v>2095.69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:G998"/>
+  <dimension ref="A1:F998"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="50.453125" customWidth="1"/>
-    <col min="8" max="26" width="8.7265625" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="50.453125" customWidth="1"/>
+    <col min="7" max="25" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
-      <c r="B1" s="31" t="s">
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.4">
+      <c r="A1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-    </row>
-    <row r="2" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="32"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-    </row>
-    <row r="4" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="4"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+    </row>
+    <row r="2" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="30"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+    </row>
+    <row r="4" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
       <c r="B4" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
-      <c r="B5" s="34" t="s">
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="36"/>
-    </row>
-    <row r="6" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6" t="s">
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="34"/>
+    </row>
+    <row r="6" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="7">
-        <v>18000</v>
+      <c r="B6" s="6">
+        <v>30000</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0</v>
       </c>
       <c r="D6" s="7">
-        <v>0</v>
+        <f t="shared" ref="D6:D9" si="0">B6-C6</f>
+        <v>30000</v>
       </c>
       <c r="E6" s="8">
-        <f t="shared" ref="E6:E9" si="0">C6-D6</f>
-        <v>18000</v>
-      </c>
-      <c r="F6" s="9">
-        <f t="shared" ref="F6:F10" si="1">IF(C6=0,0,(C6-D6)/C6)</f>
+        <f t="shared" ref="E6:E10" si="1">IF(B6=0,0,(B6-C6)/B6)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6" t="s">
+    <row r="7" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="7">
+      <c r="B7" s="6">
         <v>4200</v>
       </c>
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
       <c r="D7" s="7">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8">
         <f t="shared" si="0"/>
         <v>4200</v>
       </c>
-      <c r="F7" s="9">
+      <c r="E7" s="8">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="5"/>
-      <c r="B8" s="11" t="s">
+    <row r="8" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="7">
-        <v>0</v>
+      <c r="B8" s="6">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6">
+        <v>4000</v>
       </c>
       <c r="D8" s="7">
-        <v>1900</v>
+        <f t="shared" si="0"/>
+        <v>-4000</v>
       </c>
       <c r="E8" s="8">
-        <f t="shared" si="0"/>
-        <v>-1900</v>
-      </c>
-      <c r="F8" s="9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="5"/>
-      <c r="B9" s="11" t="s">
+    <row r="9" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="7">
-        <v>0</v>
+      <c r="B9" s="6">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6">
+        <v>800</v>
       </c>
       <c r="D9" s="7">
-        <v>800</v>
-      </c>
-      <c r="E9" s="8">
         <f t="shared" si="0"/>
         <v>-800</v>
       </c>
-      <c r="F9" s="9">
+      <c r="E9" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13" t="s">
+    <row r="10" spans="1:6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="14">
-        <f t="shared" ref="C10:E10" si="2">SUM(C6:C9)</f>
-        <v>22200</v>
-      </c>
-      <c r="D10" s="14">
+      <c r="B10" s="12">
+        <f t="shared" ref="B10:D10" si="2">SUM(B6:B9)</f>
+        <v>34200</v>
+      </c>
+      <c r="C10" s="12">
         <f t="shared" si="2"/>
-        <v>2700</v>
-      </c>
-      <c r="E10" s="14">
+        <v>4800</v>
+      </c>
+      <c r="D10" s="12">
         <f t="shared" si="2"/>
-        <v>19500</v>
-      </c>
-      <c r="F10" s="15">
+        <v>29400</v>
+      </c>
+      <c r="E10" s="13">
         <f t="shared" si="1"/>
-        <v>0.8783783783783784</v>
-      </c>
-      <c r="G10" s="16"/>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="5"/>
-      <c r="B11" s="34" t="s">
+        <v>0.85964912280701755</v>
+      </c>
+      <c r="F10" s="14"/>
+    </row>
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="36"/>
-    </row>
-    <row r="12" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="5"/>
-      <c r="B12" s="6" t="s">
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="34"/>
+    </row>
+    <row r="12" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="7">
+      <c r="B12" s="6">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6">
         <v>0</v>
       </c>
       <c r="D12" s="7">
+        <f t="shared" ref="D12:D15" si="3">B12-C12</f>
         <v>0</v>
       </c>
       <c r="E12" s="8">
-        <f t="shared" ref="E12:E15" si="3">C12-D12</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="9">
-        <f t="shared" ref="F12:F16" si="4">IF(C12=0,0,(C12-D12)/C12)</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="10" t="s">
+        <f t="shared" ref="E12:E16" si="4">IF(B12=0,0,(B12-C12)/B12)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6" t="s">
+    <row r="13" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="7">
+      <c r="B13" s="6">
         <v>1200</v>
       </c>
+      <c r="C13" s="6">
+        <v>0</v>
+      </c>
       <c r="D13" s="7">
-        <v>0</v>
-      </c>
-      <c r="E13" s="8">
         <f t="shared" si="3"/>
         <v>1200</v>
       </c>
-      <c r="F13" s="9">
+      <c r="E13" s="8">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="5"/>
-      <c r="B14" s="11" t="s">
+    <row r="14" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="7">
-        <v>0</v>
+      <c r="B14" s="6">
+        <v>0</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1800</v>
       </c>
       <c r="D14" s="7">
-        <v>1800</v>
-      </c>
-      <c r="E14" s="8">
         <f t="shared" si="3"/>
         <v>-1800</v>
       </c>
-      <c r="F14" s="9">
+      <c r="E14" s="8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="F14" s="9" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="15" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="5"/>
-      <c r="B15" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="7">
-        <v>0</v>
+      <c r="B15" s="6">
+        <v>0</v>
+      </c>
+      <c r="C15" s="6">
+        <v>650</v>
       </c>
       <c r="D15" s="7">
-        <v>650</v>
-      </c>
-      <c r="E15" s="8">
         <f t="shared" si="3"/>
         <v>-650</v>
       </c>
-      <c r="F15" s="9">
+      <c r="E15" s="8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="F15" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="12"/>
-      <c r="B16" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="14">
-        <f t="shared" ref="C16:E16" si="5">SUM(C12:C15)</f>
+      <c r="B16" s="12">
+        <f t="shared" ref="B16:D16" si="5">SUM(B12:B15)</f>
         <v>1200</v>
       </c>
-      <c r="D16" s="14">
+      <c r="C16" s="12">
         <f t="shared" si="5"/>
         <v>2450</v>
       </c>
-      <c r="E16" s="14">
+      <c r="D16" s="12">
         <f t="shared" si="5"/>
         <v>-1250</v>
       </c>
-      <c r="F16" s="15">
+      <c r="E16" s="13">
         <f t="shared" si="4"/>
         <v>-1.0416666666666667</v>
       </c>
-      <c r="G16" s="16"/>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="5"/>
-      <c r="B17" s="34" t="s">
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="34"/>
+    </row>
+    <row r="18" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="35"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="6">
+        <v>300</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7">
+        <f t="shared" ref="D18:D20" si="6">B18-C18</f>
+        <v>300</v>
+      </c>
+      <c r="E18" s="8">
+        <f t="shared" ref="E18:E21" si="7">IF(B18=0,0,(B18-C18)/B18)</f>
+        <v>1</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="7">
-        <v>3000</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0</v>
-      </c>
-      <c r="E18" s="8">
-        <f t="shared" ref="E18:E20" si="6">C18-D18</f>
-        <v>3000</v>
-      </c>
-      <c r="F18" s="9">
-        <f t="shared" ref="F18:F21" si="7">IF(C18=0,0,(C18-D18)/C18)</f>
+    </row>
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="6">
+        <v>0</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0</v>
+      </c>
+      <c r="D19" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="6">
+        <v>0</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1500</v>
+      </c>
+      <c r="D20" s="7">
+        <f t="shared" si="6"/>
+        <v>-1500</v>
+      </c>
+      <c r="E20" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="12">
+        <f t="shared" ref="B21:D21" si="8">SUM(B18:B20)</f>
+        <v>300</v>
+      </c>
+      <c r="C21" s="12">
+        <f t="shared" si="8"/>
+        <v>1500</v>
+      </c>
+      <c r="D21" s="12">
+        <f t="shared" si="8"/>
+        <v>-1200</v>
+      </c>
+      <c r="E21" s="13">
+        <f t="shared" si="7"/>
+        <v>-4</v>
+      </c>
+      <c r="F21" s="14"/>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="34"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="6">
+        <v>2800</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0</v>
+      </c>
+      <c r="D23" s="7">
+        <f t="shared" ref="D23:D27" si="9">B23-C23</f>
+        <v>2800</v>
+      </c>
+      <c r="E23" s="8">
+        <f t="shared" ref="E23:E28" si="10">IF(B23=0,0,(B23-C23)/B23)</f>
         <v>1</v>
       </c>
-      <c r="G18" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="5"/>
-      <c r="B19" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="7">
-        <v>0</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0</v>
-      </c>
-      <c r="E19" s="8">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F19" s="9">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="5"/>
-      <c r="B20" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0</v>
-      </c>
-      <c r="D20" s="7">
-        <v>1600</v>
-      </c>
-      <c r="E20" s="8">
-        <f t="shared" si="6"/>
-        <v>-1600</v>
-      </c>
-      <c r="F20" s="9">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="14">
-        <f t="shared" ref="C21:E21" si="8">SUM(C18:C20)</f>
-        <v>3000</v>
-      </c>
-      <c r="D21" s="14">
-        <f t="shared" si="8"/>
-        <v>1600</v>
-      </c>
-      <c r="E21" s="14">
-        <f t="shared" si="8"/>
-        <v>1400</v>
-      </c>
-      <c r="F21" s="15">
-        <f t="shared" si="7"/>
-        <v>0.46666666666666667</v>
-      </c>
-      <c r="G21" s="16"/>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="5"/>
-      <c r="B22" s="34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="36"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="5"/>
-      <c r="B23" s="17" t="s">
+      <c r="F23" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="7">
-        <v>0</v>
-      </c>
-      <c r="D23" s="7">
-        <v>0</v>
-      </c>
-      <c r="E23" s="8">
-        <f t="shared" ref="E23:E27" si="9">C23-D23</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="9">
-        <f t="shared" ref="F23:F28" si="10">IF(C23=0,0,(C23-D23)/C23)</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="10"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="5"/>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="6">
+        <v>0</v>
+      </c>
+      <c r="C24" s="6">
+        <v>500</v>
+      </c>
+      <c r="D24" s="7">
+        <f t="shared" si="9"/>
+        <v>-500</v>
+      </c>
+      <c r="E24" s="8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="7">
-        <v>0</v>
-      </c>
-      <c r="D24" s="7">
-        <v>280</v>
-      </c>
-      <c r="E24" s="8">
+    </row>
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="6">
+        <v>0</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0</v>
+      </c>
+      <c r="D25" s="7">
         <f t="shared" si="9"/>
-        <v>-280</v>
-      </c>
-      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="8">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="5"/>
-      <c r="B25" s="17" t="s">
+      <c r="F25" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="7">
-        <v>0</v>
-      </c>
-      <c r="D25" s="7">
-        <v>200</v>
-      </c>
-      <c r="E25" s="8">
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="6">
+        <v>420</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7">
         <f t="shared" si="9"/>
-        <v>-200</v>
-      </c>
-      <c r="F25" s="9">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="5"/>
-      <c r="B26" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="7">
-        <v>1200</v>
-      </c>
-      <c r="D26" s="7">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="E26" s="8">
-        <f t="shared" si="9"/>
-        <v>1200</v>
-      </c>
-      <c r="F26" s="9">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="G26" s="10"/>
-    </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="5"/>
-      <c r="B27" s="17" t="s">
+      <c r="F26" s="9"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" s="6">
+        <v>0</v>
+      </c>
+      <c r="C27" s="6">
+        <v>420</v>
+      </c>
+      <c r="D27" s="7">
+        <f t="shared" si="9"/>
+        <v>-420</v>
+      </c>
+      <c r="E27" s="8">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="7">
-        <v>0</v>
-      </c>
-      <c r="D27" s="7">
-        <v>0</v>
-      </c>
-      <c r="E27" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F27" s="9">
+    </row>
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="12">
+        <f t="shared" ref="B28:D28" si="11">SUM(B23:B27)</f>
+        <v>3220</v>
+      </c>
+      <c r="C28" s="12">
+        <f t="shared" si="11"/>
+        <v>920</v>
+      </c>
+      <c r="D28" s="12">
+        <f t="shared" si="11"/>
+        <v>2300</v>
+      </c>
+      <c r="E28" s="13">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="12"/>
-      <c r="B28" s="13" t="s">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="F28" s="14"/>
+    </row>
+    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="14">
-        <f t="shared" ref="C28:E28" si="11">SUM(C23:C27)</f>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="34"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="6">
         <v>1200</v>
       </c>
-      <c r="D28" s="14">
-        <f t="shared" si="11"/>
-        <v>480</v>
-      </c>
-      <c r="E28" s="14">
-        <f t="shared" si="11"/>
-        <v>720</v>
-      </c>
-      <c r="F28" s="15">
-        <f t="shared" si="10"/>
-        <v>0.6</v>
-      </c>
-      <c r="G28" s="16"/>
-    </row>
-    <row r="29" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="5"/>
-      <c r="B29" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="36"/>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="5"/>
-      <c r="B30" s="17" t="s">
+      <c r="C30" s="6">
+        <v>0</v>
+      </c>
+      <c r="D30" s="7">
+        <f t="shared" ref="D30:D36" si="12">B30-C30</f>
+        <v>1200</v>
+      </c>
+      <c r="E30" s="8">
+        <f t="shared" ref="E30:E37" si="13">IF(B30=0,0,(B30-C30)/B30)</f>
+        <v>1</v>
+      </c>
+      <c r="F30" s="9"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="7">
+      <c r="B31" s="6">
+        <v>0</v>
+      </c>
+      <c r="C31" s="6">
         <v>1200</v>
       </c>
-      <c r="D30" s="7">
-        <v>0</v>
-      </c>
-      <c r="E30" s="8">
-        <f t="shared" ref="E30:E36" si="12">C30-D30</f>
-        <v>1200</v>
-      </c>
-      <c r="F30" s="9">
-        <f t="shared" ref="F30:F37" si="13">IF(C30=0,0,(C30-D30)/C30)</f>
-        <v>1</v>
-      </c>
-      <c r="G30" s="10"/>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="5"/>
-      <c r="B31" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C31" s="7">
-        <v>0</v>
-      </c>
       <c r="D31" s="7">
-        <v>1200</v>
-      </c>
-      <c r="E31" s="8">
         <f t="shared" si="12"/>
         <v>-1200</v>
       </c>
-      <c r="F31" s="9">
+      <c r="E31" s="8">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G31" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="5"/>
-      <c r="B32" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="7">
-        <v>0</v>
+      <c r="F31" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="6">
+        <v>0</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1000</v>
       </c>
       <c r="D32" s="7">
-        <v>1000</v>
-      </c>
-      <c r="E32" s="8">
         <f t="shared" si="12"/>
         <v>-1000</v>
       </c>
-      <c r="F32" s="9">
+      <c r="E32" s="8">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G32" s="10"/>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="5"/>
-      <c r="B33" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" s="7">
-        <v>0</v>
+      <c r="F32" s="9"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="6">
+        <v>0</v>
+      </c>
+      <c r="C33" s="6">
+        <v>150</v>
       </c>
       <c r="D33" s="7">
-        <v>150</v>
-      </c>
-      <c r="E33" s="8">
         <f t="shared" si="12"/>
         <v>-150</v>
       </c>
-      <c r="F33" s="9">
+      <c r="E33" s="8">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G33" s="10"/>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="5"/>
-      <c r="B34" s="17" t="s">
+      <c r="F33" s="9"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="6">
+        <v>0</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0</v>
+      </c>
+      <c r="D34" s="7">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="E34" s="8">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="9"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B35" s="6">
+        <v>0</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0</v>
+      </c>
+      <c r="D35" s="7">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="E35" s="8">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="7">
-        <v>0</v>
-      </c>
-      <c r="D34" s="7">
-        <v>0</v>
-      </c>
-      <c r="E34" s="8">
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="6">
+        <v>0</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0</v>
+      </c>
+      <c r="D36" s="7">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="F34" s="9">
+      <c r="E36" s="8">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="G34" s="10"/>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="5"/>
-      <c r="B35" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="7">
-        <v>0</v>
-      </c>
-      <c r="D35" s="7">
-        <v>0</v>
-      </c>
-      <c r="E35" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="F35" s="9">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="G35" s="10" t="s">
+      <c r="F36" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="5"/>
-      <c r="B36" s="17" t="s">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="7">
-        <v>0</v>
-      </c>
-      <c r="D36" s="7">
-        <v>0</v>
-      </c>
-      <c r="E36" s="8">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="F36" s="9">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="12"/>
-      <c r="B37" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="14">
-        <f t="shared" ref="C37:E37" si="14">SUM(C30:C36)</f>
+      <c r="B37" s="12">
+        <f t="shared" ref="B37:D37" si="14">SUM(B30:B36)</f>
         <v>1200</v>
       </c>
-      <c r="D37" s="14">
+      <c r="C37" s="12">
         <f t="shared" si="14"/>
         <v>2350</v>
       </c>
-      <c r="E37" s="14">
+      <c r="D37" s="12">
         <f t="shared" si="14"/>
         <v>-1150</v>
       </c>
-      <c r="F37" s="15">
+      <c r="E37" s="13">
         <f t="shared" si="13"/>
         <v>-0.95833333333333337</v>
       </c>
-      <c r="G37" s="16"/>
-    </row>
-    <row r="38" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="5"/>
-      <c r="B38" s="34" t="s">
+      <c r="F37" s="14"/>
+    </row>
+    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="33"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="34"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="6">
+        <v>4350</v>
+      </c>
+      <c r="C39" s="6">
+        <v>0</v>
+      </c>
+      <c r="D39" s="7">
+        <f t="shared" ref="D39:D44" si="15">B39-C39</f>
+        <v>4350</v>
+      </c>
+      <c r="E39" s="8">
+        <f t="shared" ref="E39:E45" si="16">IF(B39=0,0,(B39-C39)/B39)</f>
+        <v>1</v>
+      </c>
+      <c r="F39" s="9"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="36"/>
-    </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="5"/>
-      <c r="B39" s="17" t="s">
+      <c r="B40" s="6">
+        <v>0</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0</v>
+      </c>
+      <c r="D40" s="7">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="E40" s="8">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="7">
-        <v>4350</v>
-      </c>
-      <c r="D39" s="7">
-        <v>0</v>
-      </c>
-      <c r="E39" s="8">
-        <f t="shared" ref="E39:E44" si="15">C39-D39</f>
-        <v>4350</v>
-      </c>
-      <c r="F39" s="9">
-        <f t="shared" ref="F39:F45" si="16">IF(C39=0,0,(C39-D39)/C39)</f>
-        <v>1</v>
-      </c>
-      <c r="G39" s="10"/>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="5"/>
-      <c r="B40" s="11" t="s">
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="7">
-        <v>0</v>
-      </c>
-      <c r="D40" s="7">
-        <v>0</v>
-      </c>
-      <c r="E40" s="8">
+      <c r="B41" s="6">
+        <v>190</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0</v>
+      </c>
+      <c r="D41" s="7">
         <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="F40" s="9">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="5"/>
-      <c r="B41" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C41" s="7">
-        <v>350</v>
-      </c>
-      <c r="D41" s="7">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="E41" s="8">
-        <f t="shared" si="15"/>
-        <v>350</v>
-      </c>
-      <c r="F41" s="9">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="G41" s="10"/>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="5"/>
-      <c r="B42" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C42" s="7">
-        <v>0</v>
+      <c r="F41" s="9"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="6">
+        <v>0</v>
+      </c>
+      <c r="C42" s="6">
+        <v>280</v>
       </c>
       <c r="D42" s="7">
-        <v>280</v>
-      </c>
-      <c r="E42" s="8">
         <f t="shared" si="15"/>
         <v>-280</v>
       </c>
-      <c r="F42" s="9">
+      <c r="E42" s="8">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G42" s="10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="5"/>
-      <c r="B43" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="7">
-        <v>0</v>
+      <c r="F42" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="6">
+        <v>0</v>
+      </c>
+      <c r="C43" s="6">
+        <v>40</v>
       </c>
       <c r="D43" s="7">
-        <v>40</v>
-      </c>
-      <c r="E43" s="8">
         <f t="shared" si="15"/>
         <v>-40</v>
       </c>
-      <c r="F43" s="9">
+      <c r="E43" s="8">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G43" s="10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="5"/>
-      <c r="B44" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C44" s="7">
-        <v>0</v>
+      <c r="F43" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="6">
+        <v>0</v>
+      </c>
+      <c r="C44" s="6">
+        <v>200</v>
       </c>
       <c r="D44" s="7">
-        <v>200</v>
-      </c>
-      <c r="E44" s="8">
         <f t="shared" si="15"/>
         <v>-200</v>
       </c>
-      <c r="F44" s="9">
+      <c r="E44" s="8">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="G44" s="10"/>
-    </row>
-    <row r="45" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="12"/>
-      <c r="B45" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C45" s="14">
-        <f t="shared" ref="C45:E45" si="17">SUM(C39:C44)</f>
-        <v>4700</v>
-      </c>
-      <c r="D45" s="14">
+      <c r="F44" s="9"/>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="12">
+        <f t="shared" ref="B45:D45" si="17">SUM(B39:B44)</f>
+        <v>4540</v>
+      </c>
+      <c r="C45" s="12">
         <f t="shared" si="17"/>
         <v>520</v>
       </c>
-      <c r="E45" s="14">
+      <c r="D45" s="12">
         <f t="shared" si="17"/>
-        <v>4180</v>
-      </c>
-      <c r="F45" s="15">
+        <v>4020</v>
+      </c>
+      <c r="E45" s="13">
         <f t="shared" si="16"/>
-        <v>0.88936170212765953</v>
-      </c>
-      <c r="G45" s="16"/>
-    </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="5"/>
-      <c r="B46" s="34" t="s">
+        <v>0.88546255506607929</v>
+      </c>
+      <c r="F45" s="14"/>
+    </row>
+    <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="33"/>
+      <c r="C46" s="33"/>
+      <c r="D46" s="33"/>
+      <c r="E46" s="33"/>
+      <c r="F46" s="34"/>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B47" s="6">
+        <v>1500</v>
+      </c>
+      <c r="C47" s="6">
+        <v>0</v>
+      </c>
+      <c r="D47" s="7">
+        <f t="shared" ref="D47:D50" si="18">B47-C47</f>
+        <v>1500</v>
+      </c>
+      <c r="E47" s="8">
+        <f t="shared" ref="E47:E51" si="19">IF(B47=0,0,(B47-C47)/B47)</f>
+        <v>1</v>
+      </c>
+      <c r="F47" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C46" s="35"/>
-      <c r="D46" s="35"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="36"/>
-    </row>
-    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="5"/>
-      <c r="B47" s="6" t="s">
+    </row>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C47" s="7">
-        <v>3500</v>
-      </c>
-      <c r="D47" s="7">
-        <v>0</v>
-      </c>
-      <c r="E47" s="8">
-        <f t="shared" ref="E47:E50" si="18">C47-D47</f>
-        <v>3500</v>
-      </c>
-      <c r="F47" s="9">
-        <f t="shared" ref="F47:F51" si="19">IF(C47=0,0,(C47-D47)/C47)</f>
-        <v>1</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="5"/>
-      <c r="B48" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" s="7">
-        <v>2800</v>
+      <c r="B48" s="6">
+        <v>1500</v>
+      </c>
+      <c r="C48" s="6">
+        <v>0</v>
       </c>
       <c r="D48" s="7">
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>1500</v>
       </c>
       <c r="E48" s="8">
-        <f t="shared" si="18"/>
-        <v>2800</v>
-      </c>
-      <c r="F48" s="9">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="G48" s="10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="5"/>
-      <c r="B49" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C49" s="7">
-        <v>800</v>
+      <c r="F48" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B49" s="6">
+        <v>1000</v>
+      </c>
+      <c r="C49" s="6">
+        <v>0</v>
       </c>
       <c r="D49" s="7">
-        <v>0</v>
+        <f t="shared" si="18"/>
+        <v>1000</v>
       </c>
       <c r="E49" s="8">
-        <f t="shared" si="18"/>
-        <v>800</v>
-      </c>
-      <c r="F49" s="9">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="G49" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="5"/>
-      <c r="B50" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C50" s="7">
+      <c r="F49" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" s="6">
         <v>600</v>
       </c>
+      <c r="C50" s="6">
+        <v>0</v>
+      </c>
       <c r="D50" s="7">
-        <v>0</v>
-      </c>
-      <c r="E50" s="8">
         <f t="shared" si="18"/>
         <v>600</v>
       </c>
-      <c r="F50" s="9">
+      <c r="E50" s="8">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="G50" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="12"/>
-      <c r="B51" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C51" s="14">
-        <f t="shared" ref="C51:E51" si="20">SUM(C47:C50)</f>
-        <v>7700</v>
-      </c>
-      <c r="D51" s="14">
+      <c r="F50" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51" s="12">
+        <f t="shared" ref="B51:D51" si="20">SUM(B47:B50)</f>
+        <v>4600</v>
+      </c>
+      <c r="C51" s="12">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="E51" s="14">
+      <c r="D51" s="12">
         <f t="shared" si="20"/>
-        <v>7700</v>
-      </c>
-      <c r="F51" s="15">
+        <v>4600</v>
+      </c>
+      <c r="E51" s="13">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="G51" s="16"/>
-    </row>
-    <row r="52" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="53" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="18"/>
-      <c r="B53" s="19" t="s">
+      <c r="F51" s="14"/>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" s="18">
+        <f t="shared" ref="B53:D53" si="21">B10+B16+B21+B28+B37+B45+B51</f>
+        <v>49260</v>
+      </c>
+      <c r="C53" s="18">
+        <f t="shared" si="21"/>
+        <v>12540</v>
+      </c>
+      <c r="D53" s="18">
+        <f t="shared" si="21"/>
+        <v>36720</v>
+      </c>
+      <c r="E53" s="19">
+        <f>IF(B53=0,0,(B53-C53)/B53)</f>
+        <v>0.74543239951278928</v>
+      </c>
+      <c r="F53" s="16"/>
+    </row>
+    <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+    </row>
+    <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C53" s="20">
-        <f t="shared" ref="C53:E53" si="21">C10+C16+C21+C28+C37+C45+C51</f>
-        <v>41200</v>
-      </c>
-      <c r="D53" s="20">
-        <f t="shared" si="21"/>
-        <v>10100</v>
-      </c>
-      <c r="E53" s="20">
-        <f t="shared" si="21"/>
-        <v>31100</v>
-      </c>
-      <c r="F53" s="21">
-        <f>IF(C53=0,0,(C53-D53)/C53)</f>
-        <v>0.75485436893203883</v>
-      </c>
-      <c r="G53" s="18"/>
-    </row>
-    <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="33" t="s">
+      <c r="B56" s="20">
+        <f>B53*12</f>
+        <v>591120</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-    </row>
-    <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="1" t="s">
+      <c r="B57" s="20">
+        <f>C53*12</f>
+        <v>150480</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="22">
-        <f>C53*12</f>
-        <v>494400</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C57" s="22">
+      <c r="B58" s="2">
         <f>D53*12</f>
-        <v>121200</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C58" s="2">
-        <f>E53*12</f>
-        <v>373200</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+        <v>440640</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -3042,17 +3260,17 @@
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B55:G55"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B29:G29"/>
+  <dataConsolidate/>
+  <mergeCells count="9">
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -3062,7 +3280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF006100"/>
@@ -3070,95 +3288,95 @@
   <dimension ref="A1:B998"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="59.08984375" customWidth="1"/>
+    <col min="1" max="1" width="48.54296875" customWidth="1"/>
     <col min="2" max="2" width="91.54296875" customWidth="1"/>
     <col min="3" max="23" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.4">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="28"/>
+    </row>
+    <row r="3" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="30"/>
-    </row>
-    <row r="3" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="23" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B4" s="9" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="24" t="s">
+    <row r="5" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="24" t="s">
+    <row r="6" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="24" t="s">
+    <row r="7" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="24" t="s">
+    <row r="8" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="24" t="s">
+    <row r="9" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="24" t="s">
+    <row r="10" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="24" t="s">
+    <row r="11" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="24" t="s">
+    <row r="12" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4153,337 +4371,322 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF2E75B6"/>
   </sheetPr>
-  <dimension ref="A1:F999"/>
+  <dimension ref="A1:E999"/>
   <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="44" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="42" customWidth="1"/>
-    <col min="7" max="26" width="8.7265625" customWidth="1"/>
+    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="6" max="25" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.4">
-      <c r="B1" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-    </row>
-    <row r="3" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="4"/>
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.4">
+      <c r="A1" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+    </row>
+    <row r="3" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="B3" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="23" x14ac:dyDescent="0.35">
+      <c r="A4" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B4" s="6">
+        <v>100</v>
+      </c>
+      <c r="C4" s="23">
+        <v>48</v>
+      </c>
+      <c r="D4" s="7">
+        <f>B4*C4</f>
+        <v>4800</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="23" x14ac:dyDescent="0.35">
-      <c r="A4" s="5"/>
-      <c r="B4" s="17" t="s">
+    <row r="5" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="7">
+      <c r="B5" s="6">
+        <v>120</v>
+      </c>
+      <c r="C5" s="23">
+        <v>120</v>
+      </c>
+      <c r="D5" s="7">
+        <f t="shared" ref="D5:D15" si="0">B5*C5</f>
+        <v>14400</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="6">
         <v>100</v>
       </c>
-      <c r="D4" s="25">
-        <v>48</v>
-      </c>
-      <c r="E4" s="8">
-        <f>C4*D4</f>
-        <v>4800</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
-      <c r="B5" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="7">
-        <v>120</v>
-      </c>
-      <c r="D5" s="25">
-        <v>120</v>
-      </c>
-      <c r="E5" s="8">
-        <f t="shared" ref="E5:E15" si="0">C5*D5</f>
-        <v>14400</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="5"/>
-      <c r="B6" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="7">
-        <v>100</v>
-      </c>
-      <c r="D6" s="25">
+      <c r="C6" s="23">
         <v>64</v>
       </c>
-      <c r="E6" s="8">
+      <c r="D6" s="7">
         <f t="shared" si="0"/>
         <v>6400</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="5"/>
-      <c r="B7" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="E6" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="6">
         <v>100</v>
       </c>
-      <c r="D7" s="25">
+      <c r="C7" s="23">
         <v>96</v>
       </c>
-      <c r="E7" s="8">
+      <c r="D7" s="7">
         <f t="shared" si="0"/>
         <v>9600</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="5"/>
-      <c r="B8" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="7">
+      <c r="E7" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="6">
         <v>120</v>
       </c>
-      <c r="D8" s="25">
+      <c r="C8" s="23">
         <v>24</v>
       </c>
-      <c r="E8" s="8">
+      <c r="D8" s="7">
         <f t="shared" si="0"/>
         <v>2880</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="5"/>
-      <c r="B9" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="7">
+      <c r="E8" s="9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" s="6">
         <v>100</v>
       </c>
-      <c r="D9" s="25">
+      <c r="C9" s="23">
         <v>16</v>
       </c>
-      <c r="E9" s="8">
+      <c r="D9" s="7">
         <f t="shared" si="0"/>
         <v>1600</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="5"/>
-      <c r="B10" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="E9" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="6">
         <v>100</v>
       </c>
-      <c r="D10" s="25">
+      <c r="C10" s="23">
         <v>32</v>
       </c>
-      <c r="E10" s="8">
+      <c r="D10" s="7">
         <f t="shared" si="0"/>
         <v>3200</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="5"/>
-      <c r="B11" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="E10" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="6">
         <v>100</v>
       </c>
-      <c r="D11" s="25">
+      <c r="C11" s="23">
         <v>12</v>
       </c>
-      <c r="E11" s="8">
+      <c r="D11" s="7">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="5"/>
-      <c r="B12" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="C12" s="7">
+      <c r="E11" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="6">
         <v>120</v>
       </c>
-      <c r="D12" s="25">
+      <c r="C12" s="23">
         <v>16</v>
       </c>
-      <c r="E12" s="8">
+      <c r="D12" s="7">
         <f t="shared" si="0"/>
         <v>1920</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="5"/>
-      <c r="B13" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="C13" s="7">
+      <c r="E12" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="6">
         <v>100</v>
       </c>
-      <c r="D13" s="25">
+      <c r="C13" s="23">
         <v>40</v>
       </c>
-      <c r="E13" s="8">
+      <c r="D13" s="7">
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="5"/>
-      <c r="B14" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="7">
+      <c r="E13" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B14" s="6">
         <v>100</v>
       </c>
-      <c r="D14" s="25">
+      <c r="C14" s="23">
         <v>24</v>
       </c>
-      <c r="E14" s="8">
+      <c r="D14" s="7">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="E14" s="9" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="6">
+        <v>0</v>
+      </c>
+      <c r="C15" s="23">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="5"/>
-      <c r="B15" s="17" t="s">
+    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="7">
-        <v>0</v>
-      </c>
-      <c r="D15" s="25">
-        <v>0</v>
-      </c>
-      <c r="E15" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="26">
-        <f t="shared" ref="D16:E16" si="1">SUM(D4:D15)</f>
+      <c r="B16" s="16"/>
+      <c r="C16" s="24">
+        <f t="shared" ref="C16:D16" si="1">SUM(C4:C15)</f>
         <v>492</v>
       </c>
-      <c r="E16" s="20">
+      <c r="D16" s="18">
         <f t="shared" si="1"/>
         <v>52400</v>
       </c>
-      <c r="F16" s="18"/>
-    </row>
-    <row r="18" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B18" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B19" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" s="2">
-        <f>'Comparativo Mensal'!E53</f>
-        <v>31100</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="27" t="s">
+      <c r="E16" s="16"/>
+    </row>
+    <row r="18" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2">
+        <f>'Comparativo Mensal'!D53</f>
+        <v>36720</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="28">
-        <f>IF(C19=0,"N/A",CEILING(E16/C19,1))</f>
+      <c r="B20" s="26">
+        <f>IF(B19=0,"N/A",CEILING(D16/B19,1))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="27" t="s">
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="29">
-        <f>IF(E16=0,0,(C19*12-E16)/E16)</f>
-        <v>6.1221374045801529</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="23" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="24" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="32" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="B21" s="27">
+        <f>IF(D16=0,0,(B19*12-D16)/D16)</f>
+        <v>7.4091603053435113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -5453,7 +5656,7 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/arch/migracao_oci_aws.xlsx
+++ b/arch/migracao_oci_aws.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\clayton.oliveira\source\repos\files\arch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2926C10-FFBC-4250-BF3A-5B684CFD06B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4655FBFB-BC49-47C7-9900-3AA590694A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Custo - OCI" sheetId="5" r:id="rId1"/>
@@ -873,15 +873,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>71955</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>68888</xdr:rowOff>
+      <xdr:rowOff>158047</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>234995</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>321513</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>30766</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -911,8 +911,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="0" y="2450138"/>
-          <a:ext cx="10296570" cy="4388812"/>
+          <a:off x="71955" y="2551721"/>
+          <a:ext cx="10312928" cy="4428154"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1386,11 +1386,11 @@
         <v>0</v>
       </c>
       <c r="C8" s="6">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="D8" s="7">
         <f t="shared" si="0"/>
-        <v>-4000</v>
+        <v>-6000</v>
       </c>
       <c r="E8" s="8">
         <f t="shared" si="1"/>
@@ -1432,15 +1432,15 @@
       </c>
       <c r="C10" s="12">
         <f t="shared" si="2"/>
-        <v>4800</v>
+        <v>6800</v>
       </c>
       <c r="D10" s="12">
         <f t="shared" si="2"/>
-        <v>29400</v>
+        <v>27400</v>
       </c>
       <c r="E10" s="13">
         <f t="shared" si="1"/>
-        <v>0.85964912280701755</v>
+        <v>0.80116959064327486</v>
       </c>
       <c r="F10" s="14"/>
     </row>
@@ -2269,15 +2269,15 @@
       </c>
       <c r="C53" s="18">
         <f t="shared" si="21"/>
-        <v>12540</v>
+        <v>14540</v>
       </c>
       <c r="D53" s="18">
         <f t="shared" si="21"/>
-        <v>36720</v>
+        <v>34720</v>
       </c>
       <c r="E53" s="19">
         <f>IF(B53=0,0,(B53-C53)/B53)</f>
-        <v>0.74543239951278928</v>
+        <v>0.7048315062931384</v>
       </c>
       <c r="F53" s="16"/>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="B57" s="20">
         <f>C53*12</f>
-        <v>150480</v>
+        <v>174480</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B58" s="2">
         <f>D53*12</f>
-        <v>440640</v>
+        <v>416640</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="B19" s="2">
         <f>'Comparativo Mensal'!D53</f>
-        <v>36720</v>
+        <v>34720</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="B21" s="27">
         <f>IF(D16=0,0,(B19*12-D16)/D16)</f>
-        <v>7.4091603053435113</v>
+        <v>6.9511450381679385</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
